--- a/data-collection/AV company list.xlsx
+++ b/data-collection/AV company list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joyjeong/Library/Mobile Documents/com~apple~CloudDocs/2026-2/INMT5518 Supply Chain Analytics/CITS5206 Capstone/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thushaminichathushika/Desktop/26S2_5206-Group1-AV-Job-Profiles/data-collection/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{5789DF77-4336-624C-8592-5EB5440F2513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{170DB926-D2CB-495E-A1CE-5BBADA2F9F95}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{994F348B-92B9-2B41-AF68-FAD330A476C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{142631DD-2435-7043-84A5-273C12F70F84}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16380" xr2:uid="{142631DD-2435-7043-84A5-273C12F70F84}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="124">
   <si>
     <t>Name</t>
   </si>
@@ -381,13 +381,46 @@
   </si>
   <si>
     <t>https://zoox.com/</t>
+  </si>
+  <si>
+    <t>https://careers.mobileye.com/jobs</t>
+  </si>
+  <si>
+    <t>ATS / HTML Parsing</t>
+  </si>
+  <si>
+    <t>https://motional.com/careers</t>
+  </si>
+  <si>
+    <t>HTML Parsing</t>
+  </si>
+  <si>
+    <t>https://momenta.cn/en/join.html</t>
+  </si>
+  <si>
+    <t>Browser Automation</t>
+  </si>
+  <si>
+    <t>https://www.nuro.ai/careers</t>
+  </si>
+  <si>
+    <t>https://jobs.nvidia.com/careers?start=0&amp;pid=893383621773&amp;sort_by=timestamp</t>
+  </si>
+  <si>
+    <t>Browser Automation (Workday)</t>
+  </si>
+  <si>
+    <t>https://pony.ai/careers</t>
+  </si>
+  <si>
+    <t>https://plus.ai/careers</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -406,6 +439,19 @@
       <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -430,10 +476,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -770,17 +818,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AD276BB-A499-0143-8A36-A874457962F8}">
   <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -800,7 +848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -817,7 +865,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -831,7 +879,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -845,7 +893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -859,7 +907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -873,7 +921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -887,7 +935,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -901,7 +949,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>28</v>
       </c>
@@ -915,7 +963,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>32</v>
       </c>
@@ -929,7 +977,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>35</v>
       </c>
@@ -943,7 +991,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>38</v>
       </c>
@@ -957,7 +1005,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>40</v>
       </c>
@@ -969,7 +1017,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>42</v>
       </c>
@@ -983,7 +1031,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>44</v>
       </c>
@@ -997,7 +1045,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>46</v>
       </c>
@@ -1011,7 +1059,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>49</v>
       </c>
@@ -1025,7 +1073,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>51</v>
       </c>
@@ -1039,7 +1087,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>52</v>
       </c>
@@ -1053,7 +1101,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>54</v>
       </c>
@@ -1067,7 +1115,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>57</v>
       </c>
@@ -1081,7 +1129,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>59</v>
       </c>
@@ -1095,7 +1143,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
@@ -1108,8 +1156,14 @@
       <c r="D23" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>65</v>
       </c>
@@ -1122,8 +1176,14 @@
       <c r="D24" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>68</v>
       </c>
@@ -1136,8 +1196,14 @@
       <c r="D25" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>70</v>
       </c>
@@ -1150,8 +1216,14 @@
       <c r="D26" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>72</v>
       </c>
@@ -1164,8 +1236,14 @@
       <c r="D27" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>74</v>
       </c>
@@ -1178,8 +1256,14 @@
       <c r="D28" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>77</v>
       </c>
@@ -1192,8 +1276,14 @@
       <c r="D29" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="E29" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>79</v>
       </c>
@@ -1207,7 +1297,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>83</v>
       </c>
@@ -1221,7 +1311,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>85</v>
       </c>
@@ -1235,7 +1325,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>88</v>
       </c>
@@ -1249,7 +1339,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>90</v>
       </c>
@@ -1263,7 +1353,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>93</v>
       </c>
@@ -1277,7 +1367,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>96</v>
       </c>
@@ -1291,7 +1381,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>98</v>
       </c>
@@ -1305,7 +1395,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>102</v>
       </c>
@@ -1319,7 +1409,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>105</v>
       </c>
@@ -1333,7 +1423,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>107</v>
       </c>
@@ -1347,7 +1437,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>109</v>
       </c>
@@ -1361,7 +1451,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>111</v>
       </c>
